--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,6 @@
           <t>注释</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>输出文件名</t>
@@ -565,8 +564,6 @@
           <t>背包表</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -607,8 +604,6 @@
           <t>Buff表</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -649,8 +644,6 @@
           <t>角色表</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -691,8 +684,6 @@
           <t>条件表</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -733,8 +724,6 @@
           <t>对话表</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -775,8 +764,6 @@
           <t>对话内容表</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -817,8 +804,6 @@
           <t>物品表</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -859,8 +844,6 @@
           <t>任务表</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -901,8 +884,86 @@
           <t>任务上下文表</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cfg.animationstate.TbAnimationstate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Animationstate</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>animationstate.xlsx</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>动画状态表</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cfg.slotstate.TbSlotstate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Slotstate</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>slotstate.xlsx</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>插槽状态表</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,6 +965,86 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cfg.scene.TbScene</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Scene</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>scene.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>场景表</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cfg.entity.TbEntity</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>entity.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>实体表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,166 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cfg.build.TbBuild</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>build.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>养成属性表</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cfg.characterlevel.TbCharacterlevel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Characterlevel</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>characterlevel.xlsx</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>角色等级表</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>cfg.skill.TbSkill</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>技能表</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>cfg.battle.TbBattle</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>battle.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>战斗表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
